--- a/public/assets/files/planificacion-base.xlsx
+++ b/public/assets/files/planificacion-base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\metalstorm\public\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C173DF8-D9D2-41FE-9462-6D9B1934E24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86543E32-D6C5-4725-9C00-8C62D4C68190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Player1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="47">
   <si>
     <t>AVIONES</t>
   </si>
@@ -155,12 +155,21 @@
   <si>
     <t>Su-34</t>
   </si>
+  <si>
+    <t>KF-21</t>
+  </si>
+  <si>
+    <t>HABILIDAD ESPECIAL</t>
+  </si>
+  <si>
+    <t>HABILIDAD PASIVA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -186,8 +195,23 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,8 +260,38 @@
         <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9900FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBBC04"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A86E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -275,11 +329,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -317,13 +423,10 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -346,6 +449,39 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,8 +704,8 @@
   <dimension ref="A1:B1038"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="15" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="15" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="14" customWidth="1"/>
     <col min="3" max="16384" width="12.5703125" style="14"/>
   </cols>
   <sheetData>
@@ -4916,346 +5052,346 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="17">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="17">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="17">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="17">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="17">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="17">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="17">
         <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="17">
         <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="17">
         <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="17">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="17">
         <v>10</v>
       </c>
     </row>
@@ -5269,356 +5405,630 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="12.5703125" style="2"/>
+    <col min="3" max="3" width="20.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="C1" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="29">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+      <c r="C2" s="30">
+        <v>2</v>
+      </c>
+      <c r="D2" s="30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="C3" s="27">
+        <v>1</v>
+      </c>
+      <c r="D3" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="C4" s="27">
+        <v>2</v>
+      </c>
+      <c r="D4" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="C5" s="27">
+        <v>1</v>
+      </c>
+      <c r="D5" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+      <c r="C6" s="27">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
+      <c r="C7" s="27">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
+      <c r="B8" s="17">
+        <v>0</v>
+      </c>
+      <c r="C8" s="27">
+        <v>0</v>
+      </c>
+      <c r="D8" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="17">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="C9" s="27">
+        <v>1</v>
+      </c>
+      <c r="D9" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
+      <c r="B10" s="17">
+        <v>0</v>
+      </c>
+      <c r="C10" s="27">
+        <v>1</v>
+      </c>
+      <c r="D10" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="17">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
+      <c r="C11" s="27">
+        <v>2</v>
+      </c>
+      <c r="D11" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="17">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+      <c r="C12" s="27">
+        <v>2</v>
+      </c>
+      <c r="D12" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+      <c r="B13" s="17">
+        <v>0</v>
+      </c>
+      <c r="C13" s="27">
+        <v>1</v>
+      </c>
+      <c r="D13" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
+      <c r="C14" s="27">
+        <v>0</v>
+      </c>
+      <c r="D14" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="17">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
+      <c r="C15" s="27">
+        <v>1</v>
+      </c>
+      <c r="D15" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="17">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
+      <c r="C16" s="27">
+        <v>1</v>
+      </c>
+      <c r="D16" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="B17" s="17">
+        <v>0</v>
+      </c>
+      <c r="C17" s="27">
+        <v>0</v>
+      </c>
+      <c r="D17" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
+      <c r="C18" s="27">
+        <v>2</v>
+      </c>
+      <c r="D18" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="17">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
+      <c r="C19" s="27">
+        <v>2</v>
+      </c>
+      <c r="D19" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="17">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19" t="s">
+      <c r="C20" s="27">
+        <v>1</v>
+      </c>
+      <c r="D20" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="17">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="C21" s="27">
+        <v>0</v>
+      </c>
+      <c r="D21" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="17">
+        <v>4</v>
+      </c>
+      <c r="C22" s="27">
+        <v>1</v>
+      </c>
+      <c r="D22" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="B23" s="17">
+        <v>20</v>
+      </c>
+      <c r="C23" s="27">
+        <v>2</v>
+      </c>
+      <c r="D23" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
+      <c r="B24" s="17">
+        <v>5</v>
+      </c>
+      <c r="C24" s="27">
+        <v>1</v>
+      </c>
+      <c r="D24" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B25" s="17">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="C25" s="27">
+        <v>0</v>
+      </c>
+      <c r="D25" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="B26" s="17">
+        <v>8</v>
+      </c>
+      <c r="C26" s="27">
+        <v>0</v>
+      </c>
+      <c r="D26" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B27" s="17">
+        <v>0</v>
+      </c>
+      <c r="C27" s="27">
+        <v>1</v>
+      </c>
+      <c r="D27" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="17">
+        <v>0</v>
+      </c>
+      <c r="C28" s="27">
+        <v>0</v>
+      </c>
+      <c r="D28" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="17">
+        <v>16</v>
+      </c>
+      <c r="C29" s="27">
+        <v>2</v>
+      </c>
+      <c r="D29" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="17">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="18">
+      <c r="C30" s="27">
+        <v>0</v>
+      </c>
+      <c r="D30" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="17">
+        <v>8</v>
+      </c>
+      <c r="C31" s="27">
+        <v>1</v>
+      </c>
+      <c r="D31" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="17">
+        <v>8</v>
+      </c>
+      <c r="C32" s="27">
+        <v>1</v>
+      </c>
+      <c r="D32" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="17">
+        <v>0</v>
+      </c>
+      <c r="C33" s="27">
+        <v>1</v>
+      </c>
+      <c r="D33" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="17">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="18">
+      <c r="C34" s="27">
+        <v>2</v>
+      </c>
+      <c r="D34" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="17">
+        <v>0</v>
+      </c>
+      <c r="C35" s="27">
+        <v>2</v>
+      </c>
+      <c r="D35" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="17">
+        <v>12</v>
+      </c>
+      <c r="C36" s="27">
+        <v>0</v>
+      </c>
+      <c r="D36" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="17">
+        <v>7</v>
+      </c>
+      <c r="C37" s="27">
+        <v>1</v>
+      </c>
+      <c r="D37" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="17">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="18">
+      <c r="C38" s="27">
+        <v>3</v>
+      </c>
+      <c r="D38" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="17">
+        <v>6</v>
+      </c>
+      <c r="C39" s="27">
+        <v>1</v>
+      </c>
+      <c r="D39" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="17">
+        <v>0</v>
+      </c>
+      <c r="C40" s="27">
+        <v>0</v>
+      </c>
+      <c r="D40" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="17">
+        <v>0</v>
+      </c>
+      <c r="C41" s="27">
+        <v>1</v>
+      </c>
+      <c r="D41" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="17">
+        <v>0</v>
+      </c>
+      <c r="C42" s="27">
+        <v>2</v>
+      </c>
+      <c r="D42" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="17">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="18">
+      <c r="C43" s="27">
+        <v>0</v>
+      </c>
+      <c r="D43" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="17">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="18">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="18">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="18">
-        <v>8</v>
+      <c r="C44" s="27">
+        <v>0</v>
+      </c>
+      <c r="D44" s="27">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
